--- a/employee_surveys/038_performance_review_check_in_form--employee_surveys.xlsx
+++ b/employee_surveys/038_performance_review_check_in_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,119 +515,115 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_1</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Performance Review Check In</t>
+          <t>What team lead am I working with during this review period?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_2</t>
+          <t>employee_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Employee Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_3</t>
+          <t>employee_title</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Team Lead</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Select the team lead you are working with</t>
-        </is>
-      </c>
+          <t>Employee Title</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_4</t>
+          <t>performance_period</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Which performance period am I being reviewed for?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_5</t>
+          <t>review_start_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Employee Title</t>
+          <t>What is the start date of this review?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,81 +635,81 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_6</t>
+          <t>review_end_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Performance Period</t>
+          <t>What is the end date of this review?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_7</t>
+          <t>review_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Review Start Date</t>
+          <t>What are some comments about this review?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_8</t>
+          <t>overall_rating_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Review End Date</t>
+          <t>How would you rate the employee's overall performance?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_9</t>
+          <t>overall_rating_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Review Comments</t>
+          <t>What specific areas for improvement would you like to focus on?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_10</t>
+          <t>overall_rating_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>What specific accomplishments or successes would you like to highlight?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,92 +745,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_11</t>
+          <t>overall_rating_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Overall Performance Rating</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>performance_review_check_in_form_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>performance_review_check_in_form_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>performance_review_check_in_form_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -849,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -877,85 +804,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_2_choices</t>
+          <t>team_lead_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>team_lead_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Team Lead 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_2_choices</t>
+          <t>team_lead_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>team_lead_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Team Lead 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_3_choices</t>
+          <t>team_lead_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>team_lead_1</t>
+          <t>team_lead_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Team Lead 1</t>
+          <t>Team Lead 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_3_choices</t>
+          <t>overall_rating_4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>team_lead_2</t>
+          <t>outstanding</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Team Lead 2</t>
+          <t>Outstanding</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>performance_review_check_in_form_3_choices</t>
+          <t>overall_rating_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>team_lead_3</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Team Lead 3</t>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>overall_rating_4_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>needs_improvement</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Needs Improvement</t>
         </is>
       </c>
     </row>
